--- a/XLSX/LoIN_15_ŠT_VVK2_NSIK_s2.xlsx
+++ b/XLSX/LoIN_15_ŠT_VVK2_NSIK_s2.xlsx
@@ -215,11 +215,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T85"/>
+  <dimension ref="A1:T105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -672,27 +672,127 @@
     <row r="2" ht="127" customHeight="1">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Funkcinės sistemos kodas - ClassificationSystem.NSIK LF arba „NSIK LF“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Funkcinės sistemos kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeLF</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK LF</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Techninės sistemos kodas - ClassificationSystem.NSIK LT arba „NSIK LT“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Techninės sistemos kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeLT</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK LT</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Komponento kodas - ClassificationSystemNSIK LK arba „NSIK LK“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Komponento kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeLK</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK LK</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Erdvės kodas - ClassificationSystem.NSIK B arba „NSIK B“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Erdvės kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeB</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK B</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Statinio kodas - ClassificationSystem.NSIK E arba „NSIK E“ klasifikatorius</t>
+          <r>
+            <t xml:space="preserve">Statinio kodas - </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>ClassificationSystem.NSIKcodeE</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> arba „</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>NSIK E</t>
+          </r>
+          <r>
+            <t>“ klasifikatorius</t>
+          </r>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -751,44 +851,38 @@
     <row r="4" outlineLevel="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Smūginė apsauga</t>
+          <t>Apsauginė sankaba</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>FNB</t>
+          <t>FNA</t>
         </is>
       </c>
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Tinklo mechaninė apsauga</t>
+          <t>Geometrinis koordinavimo elementas</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Komponentas, kurio pagrindinė funkcija – apsaugoti nuo smūginės jėgos, ją sugerti, slopinti.</t>
+          <t>Komponentas, apsaugantis nuo mechaninės jėgos, atjungiantis perdavimo mechanizmą, kai sukimo momentas viršija ribinę reikšmę.</t>
         </is>
       </c>
       <c r="I4" s="8" t="n"/>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowSegment, 
-IfcFlowSegmentType, 
-IfcFlowSegmentTypeEnum</t>
-        </is>
-      </c>
+      <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="9" t="inlineStr">
         <is>
@@ -810,524 +904,392 @@
     </row>
     <row r="5" outlineLevel="1">
       <c r="A5" s="12" t="n"/>
-      <c r="T5" s="13" t="n"/>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T5" s="14" t="n"/>
     </row>
     <row r="6" outlineLevel="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="12" t="n"/>
+      <c r="T6" s="14" t="n"/>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Smūginė apsauga</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>FNB</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Tinklo mechaninė apsauga</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Komponentas, kurio pagrindinė funkcija – apsaugoti nuo smūginės jėgos, ją sugerti, slopinti.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowSegment, 
+IfcFlowSegmentType, 
+IfcFlowSegmentTypeEnum</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="12" t="n"/>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementCommon.System</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T8" s="14" t="n"/>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="12" t="n"/>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T9" s="14" t="n"/>
+    </row>
+    <row r="10" outlineLevel="1">
+      <c r="A10" s="12" t="n"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T10" s="14" t="n"/>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="12" t="n"/>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T11" s="14" t="n"/>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="12" t="n"/>
+      <c r="T12" s="14" t="n"/>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Skysčio srauto ribotuvas</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>RNA</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Sklendė</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Inžinerinis įrenginys, ribojantis skysčio srautą.</t>
         </is>
       </c>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="10" t="n"/>
-      <c r="S6" s="10" t="n"/>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="7" outlineLevel="1">
-      <c r="A7" s="12" t="n"/>
-      <c r="T7" s="13" t="n"/>
-    </row>
-    <row r="8" outlineLevel="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="12" t="n"/>
+      <c r="T14" s="14" t="n"/>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Izoliacija</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>RQA</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Šildymo sistemos izoliacija</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Vietinį klimatą stabilizuojantis komponentas ribojant šilumos ar garso perdavimą.</t>
         </is>
       </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>IcfCovering</t>
         </is>
       </c>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="n"/>
-      <c r="S8" s="10" t="n"/>
-      <c r="T8" s="11" t="inlineStr">
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="T9" s="13" t="n"/>
-    </row>
-    <row r="10" outlineLevel="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Vamzdis</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>WPA</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Vamzdis</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Apskritos arba kampuotos standaus skerspjūvio formos komponentas, uždaroje aplinkoje nukreipiantis skysčio arba kitų medžiagų srautą.</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>IfcPipeSegment, 
-IfcPipeSegmentType</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
-      <c r="R10" s="10" t="n"/>
-      <c r="S10" s="10" t="n"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" outlineLevel="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="T11" s="13" t="n"/>
-    </row>
-    <row r="12" outlineLevel="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Bakas</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Skysčio talpa</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Uždaras stacionarus kaupimo komponentas skysčiams laikyti.</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowTerminal, 
-IfcFlowTerminalType, 
-IfcFlowTerminalTypeEnum</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="10" t="n"/>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="10" t="n"/>
-      <c r="S12" s="10" t="n"/>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" outlineLevel="1">
-      <c r="A13" s="12" t="n"/>
-      <c r="T13" s="13" t="n"/>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Šilumos akumuliavimo skysčiuose talpykla</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>CPA</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Akumuliacinė talpa</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Talpa, pripildyta skysčiu, kuriam suteikta šiluminė energija vėliau gali būti perduodama kitiems objektams.</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>IfcTank, 
-IfcTankType, 
-IfcTankTypeEnum</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="10" t="n"/>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10" t="n"/>
-      <c r="Q14" s="10" t="n"/>
-      <c r="R14" s="10" t="n"/>
-      <c r="S14" s="10" t="n"/>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1">
-      <c r="A15" s="12" t="n"/>
-      <c r="T15" s="13" t="n"/>
-    </row>
     <row r="16" outlineLevel="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Šilumokaitis</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>EGC</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Šilumokaitis</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Šildymo ir (arba) vėsinimo prietaisas, perduodantis šilumnešio ir (arba) šaltnešio energiją kitam objektui laidumu.</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>IfcHeatExchanger, 
-IfcHeatExchangerType, 
-IfcHeatExchangerTypeEnum, 
-IfcTank, 
-IfcTankType, 
-IfcTankTypeEnum</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="n"/>
-      <c r="N16" s="10" t="n"/>
-      <c r="O16" s="10" t="n"/>
-      <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="10" t="n"/>
-      <c r="R16" s="10" t="n"/>
-      <c r="S16" s="10" t="n"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T16" s="14" t="n"/>
     </row>
     <row r="17" outlineLevel="1">
       <c r="A17" s="12" t="n"/>
-      <c r="T17" s="13" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Thickness</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>The geometric thickness of the object.</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T17" s="14" t="n"/>
     </row>
     <row r="18" outlineLevel="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Skysčio uždarymo komponentas</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>QMA</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Šilumos gamybos sistemos ventilis</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Sandarių skysčio sistemų srauto perjungimo komponentas.</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>Pset_QuantityTakeOff.Area</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>Calculated area for the object.</t>
+        </is>
+      </c>
+      <c r="P18" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T18" s="14" t="n"/>
     </row>
     <row r="19" outlineLevel="1">
       <c r="A19" s="12" t="n"/>
-      <c r="T19" s="13" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T19" s="14" t="n"/>
     </row>
     <row r="20" outlineLevel="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Skysčio reguliavimo vožtuvas</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>QNA</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Šilumos gamybos sistemos reguliavimo ventilis</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Komponentas, sandariose skysčio sistemose reguliuojantis skysčio srautą.</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="10" t="n"/>
-      <c r="R20" s="10" t="n"/>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T20" s="14" t="n"/>
     </row>
     <row r="21" outlineLevel="1">
       <c r="A21" s="12" t="n"/>
-      <c r="T21" s="13" t="n"/>
+      <c r="T21" s="14" t="n"/>
     </row>
     <row r="22" outlineLevel="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Atbulinis vožtuvas</t>
+          <t>Vamzdis</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1342,27 +1304,26 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>RMA</t>
+          <t>WPA</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Šilumos gamybos sistemos atbulinis vožtuvas</t>
+          <t>Vamzdis</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Skysčių atbulinio srauto apribojimo komponentas.</t>
+          <t>Apskritos arba kampuotos standaus skerspjūvio formos komponentas, uždaroje aplinkoje nukreipiantis skysčio arba kitų medžiagų srautą.</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
+          <t>IfcPipeSegment, 
+IfcPipeSegmentType</t>
         </is>
       </c>
       <c r="K22" s="7" t="n"/>
@@ -1386,12 +1347,12 @@
     </row>
     <row r="23" outlineLevel="1">
       <c r="A23" s="12" t="n"/>
-      <c r="T23" s="13" t="n"/>
+      <c r="T23" s="14" t="n"/>
     </row>
     <row r="24" outlineLevel="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Išardoma jungtis</t>
+          <t>Bakas</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1406,26 +1367,27 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>XMA</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Išardoma vamzdžių jungtis</t>
+          <t>Skysčio talpa</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Išardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
+          <t>Uždaras stacionarus kaupimo komponentas skysčiams laikyti.</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>IfcPipeFitting, 
-IfcPipeFittingType</t>
+          <t>IfcFlowTerminal, 
+IfcFlowTerminalType, 
+IfcFlowTerminalTypeEnum</t>
         </is>
       </c>
       <c r="K24" s="7" t="n"/>
@@ -1449,12 +1411,12 @@
     </row>
     <row r="25" outlineLevel="1">
       <c r="A25" s="12" t="n"/>
-      <c r="T25" s="13" t="n"/>
+      <c r="T25" s="14" t="n"/>
     </row>
     <row r="26" outlineLevel="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Neišardoma jungtis</t>
+          <t>Šilumos akumuliavimo skysčiuose talpykla</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1469,26 +1431,27 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>XMB</t>
+          <t>CPA</t>
         </is>
       </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Neišardoma vamzdžių jungtis</t>
+          <t>Akumuliacinė talpa</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Neišardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
+          <t>Talpa, pripildyta skysčiu, kuriam suteikta šiluminė energija vėliau gali būti perduodama kitiems objektams.</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>IfcPipeFitting, 
-IfcPipeFittingType</t>
+          <t>IfcTank, 
+IfcTankType, 
+IfcTankTypeEnum</t>
         </is>
       </c>
       <c r="K26" s="7" t="n"/>
@@ -1512,12 +1475,12 @@
     </row>
     <row r="27" outlineLevel="1">
       <c r="A27" s="12" t="n"/>
-      <c r="T27" s="13" t="n"/>
+      <c r="T27" s="14" t="n"/>
     </row>
     <row r="28" outlineLevel="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Kampinė jungtis</t>
+          <t>Šilumokaitis</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1532,26 +1495,30 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>XMD</t>
+          <t>EGC</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Kampinė jungtis</t>
+          <t>Šilumokaitis</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Komponentas, skirtas sujungti ir pakeisti fluido srauto kryptį.</t>
+          <t>Šildymo ir (arba) vėsinimo prietaisas, perduodantis šilumnešio ir (arba) šaltnešio energiją kitam objektui laidumu.</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>IfcPipeFitting, 
-IfcPipeFittingType</t>
+          <t>IfcHeatExchanger, 
+IfcHeatExchangerType, 
+IfcHeatExchangerTypeEnum, 
+IfcTank, 
+IfcTankType, 
+IfcTankTypeEnum</t>
         </is>
       </c>
       <c r="K28" s="7" t="n"/>
@@ -1575,12 +1542,12 @@
     </row>
     <row r="29" outlineLevel="1">
       <c r="A29" s="12" t="n"/>
-      <c r="T29" s="13" t="n"/>
+      <c r="T29" s="14" t="n"/>
     </row>
     <row r="30" outlineLevel="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Srauto šakotuvas</t>
+          <t>Skysčio uždarymo komponentas</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1595,26 +1562,27 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>QMA</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Šakotuvas jungtis</t>
+          <t>Šilumos gamybos sistemos ventilis</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Fluido srautą skirstanti ir (ar) jungianti jungtis.</t>
+          <t>Sandarių skysčio sistemų srauto perjungimo komponentas.</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>IfcPipeFitting, 
-IfcPipeFittingType</t>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
         </is>
       </c>
       <c r="K30" s="7" t="n"/>
@@ -1638,12 +1606,12 @@
     </row>
     <row r="31" outlineLevel="1">
       <c r="A31" s="12" t="n"/>
-      <c r="T31" s="13" t="n"/>
+      <c r="T31" s="14" t="n"/>
     </row>
     <row r="32" outlineLevel="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Kompresorinė šaldymo mašina</t>
+          <t>Skysčio reguliavimo vožtuvas</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1658,28 +1626,25 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>QNA</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Kompresorinė šaldymo mašina</t>
+          <t>Šilumos gamybos sistemos reguliavimo ventilis</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Elektrinio vėsinimo komponentas, dirbantis fazių (medžiagos agregatinių būsenų) keitimo principu.</t>
+          <t>Komponentas, sandariose skysčio sistemose reguliuojantis skysčio srautą.</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>IfcHeatExchanger, 
-IfcHeatExchangerType, 
-IfcHeatExchangerTypeEnum, 
-IfcFlowController, 
+          <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
@@ -1705,12 +1670,12 @@
     </row>
     <row r="33" outlineLevel="1">
       <c r="A33" s="12" t="n"/>
-      <c r="T33" s="13" t="n"/>
+      <c r="T33" s="14" t="n"/>
     </row>
     <row r="34" outlineLevel="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Šildymo ir (arba) vėsinimo paviršius</t>
+          <t>Atbulinis vožtuvas</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1725,30 +1690,27 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>EPA</t>
+          <t>RMA</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Šildymo paviršius</t>
+          <t>Šilumos gamybos sistemos atbulinis vožtuvas</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Šildymo ir (arba) vėsinimo įrenginys, perduodantis energiją šilumai laidžiu paviršiumi.</t>
+          <t>Skysčių atbulinio srauto apribojimo komponentas.</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>IfcHeatExchanger, 
-IfcHeatExchangerType, 
-IfcHeatExchangerTypeEnum, 
-IfcTank, 
-IfcTankType, 
-IfcTankTypeEnum</t>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
         </is>
       </c>
       <c r="K34" s="7" t="n"/>
@@ -1772,12 +1734,12 @@
     </row>
     <row r="35" outlineLevel="1">
       <c r="A35" s="12" t="n"/>
-      <c r="T35" s="13" t="n"/>
+      <c r="T35" s="14" t="n"/>
     </row>
     <row r="36" outlineLevel="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Šilumos siurblys</t>
+          <t>Išardoma jungtis</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1792,27 +1754,26 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>EGA</t>
+          <t>XMA</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Šilumos siurblys</t>
+          <t>Išardoma vamzdžių jungtis</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Šiluminės energijos transformavimo įrenginys galintis gaminti šilumą ir (arba) vėsą, dirbantis Karno / garo kompresijos ciklo / absorbcijos principais.</t>
+          <t>Išardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
         </is>
       </c>
       <c r="K36" s="7" t="n"/>
@@ -1836,12 +1797,12 @@
     </row>
     <row r="37" outlineLevel="1">
       <c r="A37" s="12" t="n"/>
-      <c r="T37" s="13" t="n"/>
+      <c r="T37" s="14" t="n"/>
     </row>
     <row r="38" outlineLevel="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Teigiamo darbinio tūrio siurblys</t>
+          <t>Neišardoma jungtis</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -1856,27 +1817,26 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>GPA</t>
+          <t>XMB</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Šildymo sistemos sistemos teigiamo slėgio siurblys</t>
+          <t>Neišardoma vamzdžių jungtis</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Skysčio srautą sukuriantis komponentas, perkeliantis įtrauktą skystį į išleidimo angą.</t>
+          <t>Neišardoma vamzdyno jungtis, sujungianti uždarą srautą.</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>IfcDistributionControlElement, 
-IfcDistributionControlElementType, 
-IfcDistributionControlElementTypeEnum</t>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
         </is>
       </c>
       <c r="K38" s="7" t="n"/>
@@ -1900,12 +1860,12 @@
     </row>
     <row r="39" outlineLevel="1">
       <c r="A39" s="12" t="n"/>
-      <c r="T39" s="13" t="n"/>
+      <c r="T39" s="14" t="n"/>
     </row>
     <row r="40" outlineLevel="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Rotacinis siurblys</t>
+          <t>Kampinė jungtis</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -1920,27 +1880,26 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>GPB</t>
+          <t>XMD</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Siurblys</t>
+          <t>Kampinė jungtis</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Skysčio srautą sukuriantis komponentas, mechaniškai suteikiantis skysčiui greitį.</t>
+          <t>Komponentas, skirtas sujungti ir pakeisti fluido srauto kryptį.</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
         </is>
       </c>
       <c r="K40" s="7" t="n"/>
@@ -1964,10 +1923,14 @@
     </row>
     <row r="41" outlineLevel="1">
       <c r="A41" s="12" t="n"/>
-      <c r="T41" s="13" t="n"/>
+      <c r="T41" s="14" t="n"/>
     </row>
     <row r="42" outlineLevel="1">
-      <c r="A42" s="14" t="n"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Srauto šakotuvas</t>
+        </is>
+      </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
           <t>H</t>
@@ -1980,23 +1943,26 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>%GPB1010</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Cirkuliacinis siurblys</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
+          <t>Šakotuvas</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Fluido srautą skirstanti ir (ar) jungianti jungtis.</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="n"/>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
+          <t>IfcPipeFitting, 
+IfcPipeFittingType</t>
         </is>
       </c>
       <c r="K42" s="7" t="n"/>
@@ -2020,12 +1986,12 @@
     </row>
     <row r="43" outlineLevel="1">
       <c r="A43" s="12" t="n"/>
-      <c r="T43" s="13" t="n"/>
+      <c r="T43" s="14" t="n"/>
     </row>
     <row r="44" outlineLevel="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Apsauginis vožtuvas</t>
+          <t>Kompresorinė šaldymo mašina</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2040,27 +2006,27 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>ECC</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Apsauginis vožtuvas</t>
+          <t>Kompresorinė šaldymo mašina</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Apsauginis komponentas, išleidžiantis skystį ar garą, kai slėgis viršija nustatytą reikšmę.</t>
+          <t>Elektrinio vėsinimo komponentas, dirbantis fazių (medžiagos agregatinių būsenų) keitimo principu.</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>IfcValve, 
-IfcValveType, 
-IfcValveTypeEnum, 
+          <t>IfcHeatExchanger, 
+IfcHeatExchangerType, 
+IfcHeatExchangerTypeEnum, 
 IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
@@ -2087,12 +2053,12 @@
     </row>
     <row r="45" outlineLevel="1">
       <c r="A45" s="12" t="n"/>
-      <c r="T45" s="13" t="n"/>
+      <c r="T45" s="14" t="n"/>
     </row>
     <row r="46" outlineLevel="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Atskirtuvas</t>
+          <t>Šilumos siurblys</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2107,23 +2073,29 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>HQB</t>
+          <t>EGA</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Filtras</t>
+          <t>Šilumos siurblys</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Mechaninio atskyrimo komponentas, atskiriantis daleles atsižvelgiant į jų dydį ar formą.</t>
+          <t>Šiluminės energijos transformavimo įrenginys galintis gaminti šilumą ir (arba) vėsą, dirbantis Karno / garo kompresijos ciklo / absorbcijos principais.</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
-      <c r="J46" s="7" t="n"/>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="9" t="inlineStr">
         <is>
@@ -2145,12 +2117,12 @@
     </row>
     <row r="47" outlineLevel="1">
       <c r="A47" s="12" t="n"/>
-      <c r="T47" s="13" t="n"/>
+      <c r="T47" s="14" t="n"/>
     </row>
     <row r="48" outlineLevel="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Išsiplėtimo indas</t>
+          <t>Teigiamo darbinio tūrio siurblys</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2165,27 +2137,27 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>FLE</t>
+          <t>GPA</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>Išsiplėtimo indas</t>
+          <t>Šildymo sistemos sistemos teigiamo slėgio siurblys</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Apsauginis komponentas, apsaugantis nuo tūrinio išsiplėtimo.</t>
+          <t>Skysčio srautą sukuriantis komponentas, perkeliantis įtrauktą skystį į išleidimo angą.</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>IfcTank, 
-IfcTankType, 
-IfcTankTypeEnum</t>
+          <t>IfcDistributionControlElement, 
+IfcDistributionControlElementType, 
+IfcDistributionControlElementTypeEnum</t>
         </is>
       </c>
       <c r="K48" s="7" t="n"/>
@@ -2209,12 +2181,12 @@
     </row>
     <row r="49" outlineLevel="1">
       <c r="A49" s="12" t="n"/>
-      <c r="T49" s="13" t="n"/>
+      <c r="T49" s="14" t="n"/>
     </row>
     <row r="50" outlineLevel="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Šulinys</t>
+          <t>Rotacinis siurblys</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2229,23 +2201,29 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>XMC</t>
+          <t>GPB</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Šulinys</t>
+          <t>Siurblys</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Uždara kamera, skirta srauto jungtims ar kitoms svarbioms vietoms po žeme.</t>
+          <t>Skysčio srautą sukuriantis komponentas, mechaniškai suteikiantis skysčiui greitį.</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
-      <c r="J50" s="7" t="n"/>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
       <c r="K50" s="7" t="n"/>
       <c r="L50" s="9" t="inlineStr">
         <is>
@@ -2267,222 +2245,99 @@
     </row>
     <row r="51" outlineLevel="1">
       <c r="A51" s="12" t="n"/>
-      <c r="M51" s="15" t="inlineStr">
-        <is>
-          <t>Pset_ConstructionAdministration.SpecificationSectionNumber</t>
-        </is>
-      </c>
-      <c r="N51" s="15" t="inlineStr">
-        <is>
-          <t>A reference number to an external contract technical specification section describing either (a) minimum performance requirements of a given IfcProductType/[[IfcProduct]] or (b) a preselection for a specific IfcProductType/[[IfcProduct]] made for this project.</t>
-        </is>
-      </c>
-      <c r="P51" s="15" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="T51" s="13" t="n"/>
+      <c r="T51" s="14" t="n"/>
     </row>
     <row r="52" outlineLevel="1">
-      <c r="A52" s="12" t="n"/>
-      <c r="M52" s="15" t="inlineStr">
-        <is>
-          <t>Pset_ElementCommon.System</t>
-        </is>
-      </c>
-      <c r="N52" s="15" t="inlineStr">
-        <is>
-          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
-        </is>
-      </c>
-      <c r="P52" s="15" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="T52" s="13" t="n"/>
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>%GPB1010</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>Cirkuliacinis siurblys</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
     </row>
     <row r="53" outlineLevel="1">
       <c r="A53" s="12" t="n"/>
-      <c r="M53" s="15" t="inlineStr">
-        <is>
-          <t>Pset_ElementComponentCommon.Diameter</t>
-        </is>
-      </c>
-      <c r="N53" s="15" t="inlineStr">
-        <is>
-          <t>The [[Diameter]] of the object.</t>
-        </is>
-      </c>
-      <c r="P53" s="15" t="inlineStr">
-        <is>
-          <t>Real</t>
-        </is>
-      </c>
-      <c r="T53" s="13" t="n"/>
+      <c r="T53" s="14" t="n"/>
     </row>
     <row r="54" outlineLevel="1">
-      <c r="A54" s="12" t="n"/>
-      <c r="M54" s="15" t="inlineStr">
-        <is>
-          <t>Pset_ElementComponentCommon.Status</t>
-        </is>
-      </c>
-      <c r="N54" s="15" t="inlineStr">
-        <is>
-          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
-        </is>
-      </c>
-      <c r="P54" s="15" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="T54" s="13" t="n"/>
-    </row>
-    <row r="55" outlineLevel="1">
-      <c r="A55" s="12" t="n"/>
-      <c r="M55" s="15" t="inlineStr">
-        <is>
-          <t>Pset_QuantityTakeOff.Length</t>
-        </is>
-      </c>
-      <c r="N55" s="15" t="inlineStr">
-        <is>
-          <t>The length of the object.</t>
-        </is>
-      </c>
-      <c r="P55" s="15" t="inlineStr">
-        <is>
-          <t>Real</t>
-        </is>
-      </c>
-      <c r="T55" s="13" t="n"/>
-    </row>
-    <row r="56" outlineLevel="1">
-      <c r="A56" s="12" t="n"/>
-      <c r="M56" s="15" t="inlineStr">
-        <is>
-          <t>VVK.ElementType</t>
-        </is>
-      </c>
-      <c r="N56" s="15" t="inlineStr">
-        <is>
-          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
-        </is>
-      </c>
-      <c r="P56" s="15" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="T56" s="13" t="n"/>
-    </row>
-    <row r="57" outlineLevel="1">
-      <c r="A57" s="12" t="n"/>
-      <c r="M57" s="15" t="inlineStr">
-        <is>
-          <t>VVK.Name</t>
-        </is>
-      </c>
-      <c r="T57" s="13" t="n"/>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="A58" s="12" t="n"/>
-      <c r="T58" s="13" t="n"/>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="14" t="n"/>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Apsauginis vožtuvas</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>%CPA2010</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>Akumuliacinė talpa su elektriniu šildymo elementu</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
-      <c r="J59" s="8" t="inlineStr">
-        <is>
-          <t>IfcTank, 
-IfcTankType, 
-IfcTankTypeEnum</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="n"/>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M59" s="10" t="n"/>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="10" t="n"/>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
-      <c r="T59" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="12" t="n"/>
-      <c r="T60" s="13" t="n"/>
-    </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Sklendė</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>%QMA10</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>Sklendė</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Fluido srauto uždarymo vožtuvas.</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>Apsauginis vožtuvas</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Apsauginis komponentas, išleidžiantis skystį ar garą, kai slėgis viršija nustatytą reikšmę.</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>IfcValve, 
 IfcValveType, 
@@ -2492,923 +2347,1552 @@
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K61" s="7" t="n"/>
-      <c r="L61" s="9" t="inlineStr">
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="11" t="inlineStr">
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="62" outlineLevel="1">
-      <c r="A62" s="12" t="n"/>
-      <c r="T62" s="13" t="n"/>
-    </row>
-    <row r="63" outlineLevel="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Oro atskirtuvas</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
+    <row r="55" outlineLevel="1">
+      <c r="A55" s="12" t="n"/>
+      <c r="T55" s="14" t="n"/>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Atskirtuvas</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>%HQB40</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>Oro atskirtuvas</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>Dujų (oro) atskyrimo iš skysčių komponentas.</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="inlineStr">
-        <is>
-          <t>IfcValve, 
-IfcValveType, 
-IfcValveTypeEnum, 
-IfcFlowController, 
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>HQB</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Filtras</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Mechaninio atskyrimo komponentas, atskiriantis daleles atsižvelgiant į jų dydį ar formą.</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K63" s="7" t="n"/>
-      <c r="L63" s="9" t="inlineStr">
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M63" s="10" t="n"/>
-      <c r="N63" s="10" t="n"/>
-      <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
-      <c r="R63" s="10" t="n"/>
-      <c r="S63" s="10" t="n"/>
-      <c r="T63" s="11" t="inlineStr">
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="12" t="n"/>
-      <c r="T64" s="13" t="n"/>
-    </row>
-    <row r="65" outlineLevel="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Automatinis skysčio srauto reguliatorius</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="12" t="n"/>
+      <c r="T57" s="14" t="n"/>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Išsiplėtimo indas</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>%RNA20</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>Balansinis ventilis</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>Inžinerinis įrenginys, automatiniu būdu reguliuojantis skysčio srautą.</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="n"/>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>IfcValve, 
-IfcValveType, 
-IfcValveTypeEnum, 
-IfcFlowController, 
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>FLE</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Išsiplėtimo indas</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Apsauginis komponentas, apsaugantis nuo tūrinio išsiplėtimo.</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>IfcTank, 
+IfcTankType, 
+IfcTankTypeEnum</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="12" t="n"/>
+      <c r="T59" s="14" t="n"/>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>%CPA2010</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>Akumuliacinė talpa su elektriniu šildymo elementu</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>IfcTank, 
+IfcTankType, 
+IfcTankTypeEnum</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="12" t="n"/>
+      <c r="T61" s="14" t="n"/>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Sklendė</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>%QMA10</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>Sklendė</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Fluido srauto uždarymo vožtuvas.</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K65" s="7" t="n"/>
-      <c r="L65" s="9" t="inlineStr">
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="n"/>
-      <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="10" t="n"/>
-      <c r="R65" s="10" t="n"/>
-      <c r="S65" s="10" t="n"/>
-      <c r="T65" s="11" t="inlineStr">
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="66" outlineLevel="1">
-      <c r="A66" s="12" t="n"/>
-      <c r="T66" s="13" t="n"/>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="14" t="n"/>
-      <c r="B67" s="6" t="inlineStr">
+    <row r="63" outlineLevel="1">
+      <c r="A63" s="12" t="n"/>
+      <c r="T63" s="14" t="n"/>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Oro atskirtuvas</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>%RNA2010</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>Balansavimo ventilis su matavimo antgaliais</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>IfcValve, 
-IfcValveType, 
-IfcValveTypeEnum, 
-IfcFlowController, 
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>%HQB40</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>Oro atskirtuvas</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Dujų (oro) atskyrimo iš skysčių komponentas.</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K67" s="7" t="n"/>
-      <c r="L67" s="9" t="inlineStr">
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="11" t="inlineStr">
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="12" t="n"/>
+      <c r="T65" s="14" t="n"/>
+    </row>
+    <row r="66" outlineLevel="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Automatinis skysčio srauto reguliatorius</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>%RNA20</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>Balansinis ventilis</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Inžinerinis įrenginys, automatiniu būdu reguliuojantis skysčio srautą.</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="A67" s="12" t="n"/>
+      <c r="T67" s="14" t="n"/>
+    </row>
     <row r="68" outlineLevel="1">
-      <c r="A68" s="12" t="n"/>
-      <c r="T68" s="13" t="n"/>
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>%RNA2010</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>Balansavimo ventilis su matavimo antgaliais</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
+IfcFlowControllerType, 
+IfcFlowControllerTypeEnum</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="n"/>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
     </row>
     <row r="69" outlineLevel="1">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="12" t="n"/>
+      <c r="T69" s="14" t="n"/>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Temperatūros keitiklis</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>BTA</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Termometras</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Temperatūros jutimo komponentas su skaliariniu išėjimu.</t>
         </is>
       </c>
-      <c r="I69" s="8" t="n"/>
-      <c r="J69" s="8" t="inlineStr">
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="inlineStr">
         <is>
           <t>IfcFlowMeter, 
 IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
+IfcFlowMeterTypeEnum</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="n"/>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="A71" s="12" t="n"/>
+      <c r="T71" s="14" t="n"/>
+    </row>
+    <row r="72" outlineLevel="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Srauto energijos skaitiklis</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>BHA</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Srauto skaitiklis</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Energijos jutimo komponentas, skirtas atitinkamo energijos tankio srautui matuoti.</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowMeter, 
+IfcFlowMeterType, 
+IfcFlowMeterTypeEnum</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="12" t="n"/>
+      <c r="T73" s="14" t="n"/>
+    </row>
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Vandens skaitiklis</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>%BHA20</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>Vandens skaitiklis</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Švaraus vandens srauto apskaitos komponentas.</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="n"/>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowMeter, 
+IfcFlowMeterType, 
+IfcFlowMeterTypeEnum</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="n"/>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="10" t="n"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="12" t="n"/>
+      <c r="T75" s="14" t="n"/>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Šiluminės energijos skaitiklis</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>BHB</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>Šiluminės energijos skaitiklis</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Energijos jutimo komponentas, skirtas atitinkamam šiluminės talpos šilumos srautui matuoti.</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowMeter, 
+IfcFlowMeterType, 
+IfcFlowMeterTypeEnum</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="12" t="n"/>
+      <c r="T77" s="14" t="n"/>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Elektros energijos skaitiklis</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>BHC</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>Elektros skaitiklis</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Energijos jutimo komponentas elektros energijos srautui matuoti.</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowMeter, 
+IfcFlowMeterType, 
+IfcFlowMeterTypeEnum</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="n"/>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="12" t="n"/>
+      <c r="T79" s="14" t="n"/>
+    </row>
+    <row r="80" outlineLevel="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Absoliučiojo slėgio keitiklis</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>BPA</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Manometras</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Vieno sensoriaus absoliučiojo slėgio jutimo komponentas su skaliariniu išėjimu.</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K69" s="7" t="n"/>
-      <c r="L69" s="9" t="inlineStr">
+      <c r="K80" s="7" t="n"/>
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="11" t="inlineStr">
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="70" outlineLevel="1">
-      <c r="A70" s="12" t="n"/>
-      <c r="T70" s="13" t="n"/>
-    </row>
-    <row r="71" outlineLevel="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Srauto energijos skaitiklis</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="12" t="n"/>
+      <c r="T81" s="14" t="n"/>
+    </row>
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="15" t="n"/>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>BHA</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="n"/>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>Srauto skaitiklis</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Energijos jutimo komponentas, skirtas atitinkamo energijos tankio srautui matuoti.</t>
-        </is>
-      </c>
-      <c r="I71" s="8" t="n"/>
-      <c r="J71" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowMeter, 
-IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>BPP</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Slėgio relė</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowController, 
 IfcFlowControllerType, 
 IfcFlowControllerTypeEnum</t>
         </is>
       </c>
-      <c r="K71" s="7" t="n"/>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="K82" s="7" t="n"/>
+      <c r="L82" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="11" t="inlineStr">
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="10" t="n"/>
+      <c r="R82" s="10" t="n"/>
+      <c r="S82" s="10" t="n"/>
+      <c r="T82" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="72" outlineLevel="1">
-      <c r="A72" s="12" t="n"/>
-      <c r="T72" s="13" t="n"/>
-    </row>
-    <row r="73" outlineLevel="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Vandens skaitiklis</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+    <row r="83" outlineLevel="1">
+      <c r="A83" s="12" t="n"/>
+      <c r="T83" s="14" t="n"/>
+    </row>
+    <row r="84" outlineLevel="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Šulinys</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>%BHA20</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>Vandens skaitiklis</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Švaraus vandens srauto apskaitos komponentas.</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowMeter, 
-IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K73" s="7" t="n"/>
-      <c r="L73" s="9" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>XMC</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="7" t="n"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Šulinys</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Uždara kamera, skirta srauto jungtims ar kitoms svarbioms vietoms po žeme.</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowTerminal, 
+IfcFlowTerminalType, 
+IfcFlowTerminalTypeEnum</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="n"/>
+      <c r="L84" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="11" t="inlineStr">
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="12" t="n"/>
-      <c r="T74" s="13" t="n"/>
-    </row>
-    <row r="75" outlineLevel="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Šiluminės energijos skaitiklis</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
+    <row r="85" outlineLevel="1">
+      <c r="A85" s="12" t="n"/>
+      <c r="M85" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementCommon.System</t>
+        </is>
+      </c>
+      <c r="N85" s="13" t="inlineStr">
+        <is>
+          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+        </is>
+      </c>
+      <c r="P85" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T85" s="14" t="n"/>
+    </row>
+    <row r="86" outlineLevel="1">
+      <c r="A86" s="12" t="n"/>
+      <c r="M86" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N86" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P86" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T86" s="14" t="n"/>
+    </row>
+    <row r="87" outlineLevel="1">
+      <c r="A87" s="12" t="n"/>
+      <c r="M87" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N87" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P87" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T87" s="14" t="n"/>
+    </row>
+    <row r="88" outlineLevel="1">
+      <c r="A88" s="12" t="n"/>
+      <c r="M88" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N88" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P88" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T88" s="14" t="n"/>
+    </row>
+    <row r="89" outlineLevel="1">
+      <c r="A89" s="12" t="n"/>
+      <c r="T89" s="14" t="n"/>
+    </row>
+    <row r="90" outlineLevel="1">
+      <c r="A90" s="15" t="n"/>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>BHB</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>Šiluminės energijos skaitiklis</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Energijos jutimo komponentas, skirtas atitinkamam šiluminės talpos šilumos srautui matuoti.</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="n"/>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowMeter, 
-IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K75" s="7" t="n"/>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>%XMC1010</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>Šilumos tinklų kamera</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>IfcFlowTerminal, 
+IfcFlowTerminalType, 
+IfcFlowTerminalTypeEnum</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="n"/>
+      <c r="L90" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M75" s="10" t="n"/>
-      <c r="N75" s="10" t="n"/>
-      <c r="O75" s="10" t="n"/>
-      <c r="P75" s="10" t="n"/>
-      <c r="Q75" s="10" t="n"/>
-      <c r="R75" s="10" t="n"/>
-      <c r="S75" s="10" t="n"/>
-      <c r="T75" s="11" t="inlineStr">
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="76" outlineLevel="1">
-      <c r="A76" s="12" t="n"/>
-      <c r="T76" s="13" t="n"/>
-    </row>
-    <row r="77" outlineLevel="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Elektros energijos skaitiklis</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+    <row r="91" outlineLevel="1">
+      <c r="A91" s="12" t="n"/>
+      <c r="M91" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementCommon.System</t>
+        </is>
+      </c>
+      <c r="N91" s="13" t="inlineStr">
+        <is>
+          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+        </is>
+      </c>
+      <c r="P91" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T91" s="14" t="n"/>
+    </row>
+    <row r="92" outlineLevel="1">
+      <c r="A92" s="12" t="n"/>
+      <c r="M92" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N92" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P92" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T92" s="14" t="n"/>
+    </row>
+    <row r="93" outlineLevel="1">
+      <c r="A93" s="12" t="n"/>
+      <c r="M93" s="13" t="inlineStr">
+        <is>
+          <t>VVK.ElementType</t>
+        </is>
+      </c>
+      <c r="N93" s="13" t="inlineStr">
+        <is>
+          <t>The type denotes a particular type that indicates the object further. The use has to be established at the level of instantiable subtypes. In particular it holds the user defined type, if the enumeration of the attribute 'PredefinedType' is set to [[USERDEFINED]].</t>
+        </is>
+      </c>
+      <c r="P93" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T93" s="14" t="n"/>
+    </row>
+    <row r="94" outlineLevel="1">
+      <c r="A94" s="12" t="n"/>
+      <c r="M94" s="13" t="inlineStr">
+        <is>
+          <t>VVK.Name</t>
+        </is>
+      </c>
+      <c r="N94" s="13" t="inlineStr">
+        <is>
+          <t>Optional name for use by the participating software systems or users. For some subtypes of [[IfcRoot]] the insertion of the [[Name]] attribute may be required. This would be enforced by a where rule.</t>
+        </is>
+      </c>
+      <c r="P94" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T94" s="14" t="n"/>
+    </row>
+    <row r="95" outlineLevel="1">
+      <c r="A95" s="12" t="n"/>
+      <c r="T95" s="14" t="n"/>
+    </row>
+    <row r="96" outlineLevel="1">
+      <c r="A96" s="15" t="n"/>
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>BHC</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>Elektros skaitiklis</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Energijos jutimo komponentas elektros energijos srautui matuoti.</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="n"/>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowMeter, 
-IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K77" s="7" t="n"/>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="12" t="n"/>
-      <c r="T78" s="13" t="n"/>
-    </row>
-    <row r="79" outlineLevel="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Absoliučiojo slėgio keitiklis</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>BPA</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="n"/>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>Manometras</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>Vieno sensoriaus absoliučiojo slėgio jutimo komponentas su skaliariniu išėjimu.</t>
-        </is>
-      </c>
-      <c r="I79" s="8" t="n"/>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowMeter, 
-IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K79" s="7" t="n"/>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="10" t="n"/>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
-      <c r="T79" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" outlineLevel="1">
-      <c r="A80" s="12" t="n"/>
-      <c r="T80" s="13" t="n"/>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="14" t="n"/>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>BPP</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="n"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>Slėgio relė</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="8" t="n"/>
-      <c r="J81" s="8" t="inlineStr">
-        <is>
-          <t>IfcFlowMeter, 
-IfcFlowMeterType, 
-IfcFlowMeterTypeEnum, 
-IfcFlowController, 
-IfcFlowControllerType, 
-IfcFlowControllerTypeEnum</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="n"/>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>LoG 2</t>
-        </is>
-      </c>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="n"/>
-      <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
-      <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="11" t="inlineStr">
-        <is>
-          <t>ŠT</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="A82" s="12" t="n"/>
-      <c r="T82" s="13" t="n"/>
-    </row>
-    <row r="83" outlineLevel="1">
-      <c r="A83" s="14" t="n"/>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="n"/>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>%DCB1000</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="n"/>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>Elemento aptarnavimo erdvė</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="n"/>
-      <c r="I83" s="7" t="n"/>
-      <c r="J83" s="8" t="inlineStr">
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>DCB</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="n"/>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>Šilumos tinklo apsaugos zona</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
+      <c r="J96" s="8" t="inlineStr">
         <is>
           <t>IfcSpace, 
 IfcSpaceType</t>
         </is>
       </c>
-      <c r="K83" s="7" t="n"/>
-      <c r="L83" s="9" t="inlineStr">
+      <c r="K96" s="7" t="n"/>
+      <c r="L96" s="9" t="inlineStr">
         <is>
           <t>LoG 2</t>
         </is>
       </c>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="11" t="inlineStr">
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="11" t="inlineStr">
         <is>
           <t>ŠT</t>
         </is>
       </c>
     </row>
-    <row r="84" outlineLevel="1">
-      <c r="A84" s="12" t="n"/>
-      <c r="T84" s="13" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="16" t="n"/>
-      <c r="B85" s="17" t="n"/>
-      <c r="C85" s="17" t="n"/>
-      <c r="D85" s="17" t="n"/>
-      <c r="E85" s="17" t="n"/>
-      <c r="F85" s="17" t="n"/>
-      <c r="G85" s="17" t="n"/>
-      <c r="H85" s="17" t="n"/>
-      <c r="I85" s="17" t="n"/>
-      <c r="J85" s="17" t="n"/>
-      <c r="K85" s="17" t="n"/>
-      <c r="L85" s="17" t="n"/>
-      <c r="M85" s="17" t="n"/>
-      <c r="N85" s="17" t="n"/>
-      <c r="O85" s="17" t="n"/>
-      <c r="P85" s="17" t="n"/>
-      <c r="Q85" s="17" t="n"/>
-      <c r="R85" s="17" t="n"/>
-      <c r="S85" s="17" t="n"/>
-      <c r="T85" s="18" t="n"/>
+    <row r="97" outlineLevel="1">
+      <c r="A97" s="12" t="n"/>
+      <c r="M97" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementCommon.System</t>
+        </is>
+      </c>
+      <c r="N97" s="13" t="inlineStr">
+        <is>
+          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+        </is>
+      </c>
+      <c r="P97" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T97" s="14" t="n"/>
+    </row>
+    <row r="98" outlineLevel="1">
+      <c r="A98" s="12" t="n"/>
+      <c r="M98" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N98" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P98" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T98" s="14" t="n"/>
+    </row>
+    <row r="99" outlineLevel="1">
+      <c r="A99" s="12" t="n"/>
+      <c r="M99" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Width</t>
+        </is>
+      </c>
+      <c r="N99" s="13" t="inlineStr">
+        <is>
+          <t>The width of the object. Only given, if the object has constant thickness (prismatic).</t>
+        </is>
+      </c>
+      <c r="P99" s="13" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="T99" s="14" t="n"/>
+    </row>
+    <row r="100" outlineLevel="1">
+      <c r="A100" s="12" t="n"/>
+      <c r="T100" s="14" t="n"/>
+    </row>
+    <row r="101" outlineLevel="1">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>%DCB1001</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="n"/>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Šilumos tinklų įrenginių aptarnavimo erdvė</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>IfcSpace, 
+IfcSpaceType</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="n"/>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>LoG 2</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n"/>
+      <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="11" t="inlineStr">
+        <is>
+          <t>ŠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" outlineLevel="1">
+      <c r="A102" s="12" t="n"/>
+      <c r="M102" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementCommon.System</t>
+        </is>
+      </c>
+      <c r="N102" s="13" t="inlineStr">
+        <is>
+          <t>The building service system that requires the provision for voids, e.g. 'Air Conditioning', 'Plumbing', 'Electro', etc.</t>
+        </is>
+      </c>
+      <c r="P102" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T102" s="14" t="n"/>
+    </row>
+    <row r="103" outlineLevel="1">
+      <c r="A103" s="12" t="n"/>
+      <c r="M103" s="13" t="inlineStr">
+        <is>
+          <t>Pset_ElementComponentCommon.Status</t>
+        </is>
+      </c>
+      <c r="N103" s="13" t="inlineStr">
+        <is>
+          <t>[[Status]] of the element, predominately used in renovation or retrofitting projects. The status can be assigned to as 'New' - element designed as new addition, 'Existing' - element exists and remains, 'Demolish' - element existed but is to be demolished, 'Temporary' - element will exists only temporary (like a temporary support structure).</t>
+        </is>
+      </c>
+      <c r="P103" s="13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T103" s="14" t="n"/>
+    </row>
+    <row r="104" outlineLevel="1">
+      <c r="A104" s="12" t="n"/>
+      <c r="T104" s="14" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="n"/>
+      <c r="B105" s="17" t="n"/>
+      <c r="C105" s="17" t="n"/>
+      <c r="D105" s="17" t="n"/>
+      <c r="E105" s="17" t="n"/>
+      <c r="F105" s="17" t="n"/>
+      <c r="G105" s="17" t="n"/>
+      <c r="H105" s="17" t="n"/>
+      <c r="I105" s="17" t="n"/>
+      <c r="J105" s="17" t="n"/>
+      <c r="K105" s="17" t="n"/>
+      <c r="L105" s="17" t="n"/>
+      <c r="M105" s="17" t="n"/>
+      <c r="N105" s="17" t="n"/>
+      <c r="O105" s="17" t="n"/>
+      <c r="P105" s="17" t="n"/>
+      <c r="Q105" s="17" t="n"/>
+      <c r="R105" s="17" t="n"/>
+      <c r="S105" s="17" t="n"/>
+      <c r="T105" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="491">
+  <mergeCells count="517">
     <mergeCell ref="I32:I33"/>
     <mergeCell ref="K32:K33"/>
-    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="J60:J61"/>
     <mergeCell ref="K26:K27"/>
+    <mergeCell ref="T78:T79"/>
+    <mergeCell ref="G82:G83"/>
     <mergeCell ref="B42:B43"/>
+    <mergeCell ref="T50:T51"/>
     <mergeCell ref="T44:T45"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="T79:T80"/>
-    <mergeCell ref="T73:T74"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T81:T82"/>
-    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="T80:T81"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="K52:K53"/>
     <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="B64:B65"/>
     <mergeCell ref="H28:H29"/>
-    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="B84:B89"/>
+    <mergeCell ref="F15:F21"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="J73:J74"/>
     <mergeCell ref="B26:B27"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="T63:T64"/>
-    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="C101:C104"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="A70:A71"/>
     <mergeCell ref="T38:T39"/>
-    <mergeCell ref="J77:J78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="T74:T75"/>
+    <mergeCell ref="L7:L12"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="L68:L69"/>
     <mergeCell ref="T40:T41"/>
-    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="A84:A89"/>
     <mergeCell ref="E38:E39"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="K71:K72"/>
-    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A74:A75"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="K46:K47"/>
     <mergeCell ref="K40:K41"/>
-    <mergeCell ref="D12:D13"/>
     <mergeCell ref="C46:C47"/>
     <mergeCell ref="C40:C41"/>
     <mergeCell ref="E46:E47"/>
-    <mergeCell ref="T69:T70"/>
     <mergeCell ref="E40:E41"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="A76:A77"/>
     <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C76:C77"/>
     <mergeCell ref="I48:I49"/>
     <mergeCell ref="K48:K49"/>
-    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="T84:T89"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="E81:E82"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G90:G95"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I90:I95"/>
+    <mergeCell ref="L101:L104"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="D80:D81"/>
     <mergeCell ref="G38:G39"/>
-    <mergeCell ref="K59:K60"/>
-    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="T71:T72"/>
+    <mergeCell ref="J84:J89"/>
+    <mergeCell ref="L74:L75"/>
     <mergeCell ref="J24:J25"/>
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="G28:G29"/>
-    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="H60:H61"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="C36:C37"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="G80:G81"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="L26:L27"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G79:G80"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="K73:K74"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="T77:T78"/>
-    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="T66:T67"/>
     <mergeCell ref="C48:C49"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="L77:L78"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="I81:I82"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="K7:K12"/>
     <mergeCell ref="J42:J43"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="H78:H79"/>
     <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I76:I77"/>
     <mergeCell ref="J44:J45"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="F80:F81"/>
     <mergeCell ref="B46:B47"/>
-    <mergeCell ref="J6:J7"/>
     <mergeCell ref="D46:D47"/>
-    <mergeCell ref="T59:T60"/>
     <mergeCell ref="E34:E35"/>
-    <mergeCell ref="H73:H74"/>
     <mergeCell ref="G34:G35"/>
     <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A66:A67"/>
     <mergeCell ref="L24:L25"/>
     <mergeCell ref="I28:I29"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="D48:D49"/>
-    <mergeCell ref="T61:T62"/>
-    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="A7:A12"/>
     <mergeCell ref="T26:T27"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="K67:K68"/>
-    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="E61:E62"/>
     <mergeCell ref="H32:H33"/>
-    <mergeCell ref="L65:L66"/>
     <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="F90:F95"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H90:H95"/>
+    <mergeCell ref="K101:K104"/>
+    <mergeCell ref="E101:E104"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="B96:B100"/>
+    <mergeCell ref="D96:D100"/>
+    <mergeCell ref="T52:T53"/>
+    <mergeCell ref="T7:T12"/>
+    <mergeCell ref="B66:B67"/>
     <mergeCell ref="T24:T25"/>
-    <mergeCell ref="T18:T19"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="G84:G89"/>
+    <mergeCell ref="I84:I89"/>
     <mergeCell ref="D22:D23"/>
-    <mergeCell ref="L75:L76"/>
-    <mergeCell ref="A50:A58"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="L83:L84"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="H50:H51"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="I26:I27"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="H79:H80"/>
-    <mergeCell ref="K77:K78"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="A96:A100"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="A15:A21"/>
     <mergeCell ref="J32:J33"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="L38:L39"/>
@@ -3416,337 +3900,391 @@
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="K42:K43"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="T75:T76"/>
     <mergeCell ref="T46:T47"/>
-    <mergeCell ref="B50:B58"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="B54:B55"/>
     <mergeCell ref="L40:L41"/>
     <mergeCell ref="G44:G45"/>
+    <mergeCell ref="I50:I51"/>
     <mergeCell ref="I44:I45"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="F63:F64"/>
     <mergeCell ref="F34:F35"/>
-    <mergeCell ref="H63:H64"/>
     <mergeCell ref="A48:A49"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="I72:I73"/>
     <mergeCell ref="K1:K2"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="J96:J100"/>
+    <mergeCell ref="T96:T100"/>
+    <mergeCell ref="L96:L100"/>
+    <mergeCell ref="B101:B104"/>
+    <mergeCell ref="D101:D104"/>
+    <mergeCell ref="F101:F104"/>
+    <mergeCell ref="C96:C100"/>
     <mergeCell ref="L22:L23"/>
     <mergeCell ref="L34:L35"/>
     <mergeCell ref="I38:I39"/>
-    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="C15:C21"/>
+    <mergeCell ref="H84:H89"/>
+    <mergeCell ref="A68:A69"/>
     <mergeCell ref="L46:L47"/>
-    <mergeCell ref="K83:K84"/>
-    <mergeCell ref="D50:D58"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="E58:E59"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="J48:J49"/>
     <mergeCell ref="T48:T49"/>
+    <mergeCell ref="E52:E53"/>
     <mergeCell ref="L48:L49"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="T68:T69"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B15:B21"/>
+    <mergeCell ref="D15:D21"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="A101:A104"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="H7:H12"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="J7:J12"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J67:J68"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="T67:T68"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="G71:G72"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="K16:K17"/>
     <mergeCell ref="L36:L37"/>
-    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="J72:J73"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="T101:T104"/>
+    <mergeCell ref="I96:I100"/>
+    <mergeCell ref="T62:T63"/>
+    <mergeCell ref="K96:K100"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="F70:F71"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="K22:K23"/>
-    <mergeCell ref="J50:J58"/>
-    <mergeCell ref="L50:L58"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K90:K95"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="C90:C95"/>
+    <mergeCell ref="E90:E95"/>
+    <mergeCell ref="T76:T77"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="L56:L57"/>
     <mergeCell ref="K38:K39"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="C28:C29"/>
-    <mergeCell ref="L67:L68"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A82:A83"/>
     <mergeCell ref="A30:A31"/>
-    <mergeCell ref="T10:T11"/>
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="I54:I55"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="J83:J84"/>
-    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="G7:G12"/>
     <mergeCell ref="F42:F43"/>
-    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="T64:T65"/>
+    <mergeCell ref="I7:I12"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="D78:D79"/>
     <mergeCell ref="B28:B29"/>
-    <mergeCell ref="G18:G19"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="K61:K62"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="T72:T73"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="I82:I83"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="F73:F74"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="H48:H49"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="T82:T83"/>
+    <mergeCell ref="J15:J21"/>
+    <mergeCell ref="L82:L83"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="L15:L21"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="K50:K58"/>
-    <mergeCell ref="T83:T84"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D90:D95"/>
+    <mergeCell ref="G101:G104"/>
+    <mergeCell ref="I101:I104"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="C84:C89"/>
+    <mergeCell ref="E84:E89"/>
+    <mergeCell ref="I15:I21"/>
+    <mergeCell ref="K15:K21"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="C32:C33"/>
+    <mergeCell ref="L72:L73"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="H14:H15"/>
     <mergeCell ref="D30:D31"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="L70:L71"/>
     <mergeCell ref="C34:C35"/>
-    <mergeCell ref="G77:G78"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="D81:D82"/>
     <mergeCell ref="H38:H39"/>
     <mergeCell ref="C42:C43"/>
-    <mergeCell ref="L71:L72"/>
     <mergeCell ref="J38:J39"/>
     <mergeCell ref="E42:E43"/>
-    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="F74:F75"/>
     <mergeCell ref="G42:G43"/>
-    <mergeCell ref="T50:T58"/>
-    <mergeCell ref="K75:K76"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="C50:C51"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="C44:C45"/>
-    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="D76:D77"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="K70:K71"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="I24:I25"/>
     <mergeCell ref="D28:D29"/>
+    <mergeCell ref="T15:T21"/>
+    <mergeCell ref="T70:T71"/>
+    <mergeCell ref="L60:L61"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A4:A5"/>
     <mergeCell ref="T22:T23"/>
     <mergeCell ref="B36:B37"/>
+    <mergeCell ref="E72:E73"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="D42:D43"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="K65:K66"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="J90:J95"/>
+    <mergeCell ref="T90:T95"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="H101:H104"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="L78:L79"/>
     <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K60:K61"/>
     <mergeCell ref="L28:L29"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="D84:D89"/>
+    <mergeCell ref="F84:F89"/>
     <mergeCell ref="J30:J31"/>
+    <mergeCell ref="B4:B6"/>
     <mergeCell ref="L30:L31"/>
-    <mergeCell ref="J79:J80"/>
-    <mergeCell ref="L8:L9"/>
     <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="L79:L80"/>
-    <mergeCell ref="L73:L74"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="G20:G21"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="G14:G15"/>
     <mergeCell ref="D24:D25"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C52:C53"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="K78:K79"/>
+    <mergeCell ref="F82:F83"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="E22:E23"/>
+    <mergeCell ref="L90:L95"/>
     <mergeCell ref="G46:G47"/>
     <mergeCell ref="T36:T37"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="I46:I47"/>
+    <mergeCell ref="D50:D51"/>
     <mergeCell ref="D44:D45"/>
     <mergeCell ref="I40:I41"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="F7:F12"/>
     <mergeCell ref="H34:H35"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="K4:K6"/>
     <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="H61:H62"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="T12:T13"/>
     <mergeCell ref="H36:H37"/>
+    <mergeCell ref="D72:D73"/>
     <mergeCell ref="J36:J37"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="L81:L82"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="E96:E100"/>
+    <mergeCell ref="J101:J104"/>
+    <mergeCell ref="G96:G100"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="T56:T57"/>
+    <mergeCell ref="L84:L89"/>
     <mergeCell ref="G22:G23"/>
-    <mergeCell ref="D63:D64"/>
     <mergeCell ref="D38:D39"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="H50:H58"/>
-    <mergeCell ref="F16:F17"/>
     <mergeCell ref="G36:G37"/>
+    <mergeCell ref="K80:K81"/>
     <mergeCell ref="D40:D41"/>
     <mergeCell ref="I30:I31"/>
     <mergeCell ref="F40:F41"/>
     <mergeCell ref="K30:K31"/>
-    <mergeCell ref="K79:K80"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="H83:H84"/>
     <mergeCell ref="J34:J35"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="K81:K82"/>
+    <mergeCell ref="B58:B59"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B60:B61"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="L42:L43"/>
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E54:E55"/>
     <mergeCell ref="L44:L45"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="H80:H81"/>
     <mergeCell ref="F46:F47"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="I34:I35"/>
+    <mergeCell ref="H62:H63"/>
     <mergeCell ref="K34:K35"/>
+    <mergeCell ref="J62:J63"/>
     <mergeCell ref="K28:K29"/>
+    <mergeCell ref="E66:E67"/>
     <mergeCell ref="T32:T33"/>
-    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C7:C12"/>
     <mergeCell ref="T28:T29"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="E7:E12"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="J4:J6"/>
     <mergeCell ref="T30:T31"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="L32:L33"/>
+    <mergeCell ref="E82:E83"/>
     <mergeCell ref="I36:I37"/>
-    <mergeCell ref="B8:B9"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="T65:T66"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="G50:G58"/>
-    <mergeCell ref="I50:I58"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="T58:T59"/>
+    <mergeCell ref="F96:F100"/>
+    <mergeCell ref="H96:H100"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="H15:H21"/>
+    <mergeCell ref="T60:T61"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="K84:K89"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="L50:L51"/>
     <mergeCell ref="T34:T35"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="C64:C65"/>
     <mergeCell ref="T42:T43"/>
-    <mergeCell ref="J81:J82"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="E15:E21"/>
+    <mergeCell ref="G15:G21"/>
     <mergeCell ref="K36:K37"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A60:A61"/>
     <mergeCell ref="C26:C27"/>
-    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="K50:K51"/>
     <mergeCell ref="K44:K45"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="L63:L64"/>
-    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="J80:J81"/>
     <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="T4:T6"/>
+    <mergeCell ref="D7:D12"/>
     <mergeCell ref="A42:A43"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="I64:I65"/>
     <mergeCell ref="J46:J47"/>
-    <mergeCell ref="D67:D68"/>
     <mergeCell ref="A44:A45"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D82:D83"/>
     <mergeCell ref="K24:K25"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="A73:A74"/>
     <mergeCell ref="C24:C25"/>
     <mergeCell ref="E24:E25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
